--- a/artfynd/A 27533-2024 artfynd.xlsx
+++ b/artfynd/A 27533-2024 artfynd.xlsx
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118330819</v>
+        <v>118330815</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,25 +2358,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638774</v>
+        <v>638768</v>
       </c>
       <c r="R18" t="n">
-        <v>7036029</v>
+        <v>7036033</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118330820</v>
+        <v>118330814</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,50 +2460,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638761</v>
+        <v>638757</v>
       </c>
       <c r="R19" t="n">
-        <v>7036040</v>
+        <v>7036093</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2532,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2563,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118330815</v>
+        <v>118330819</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2575,25 +2562,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2603,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638768</v>
+        <v>638774</v>
       </c>
       <c r="R20" t="n">
-        <v>7036033</v>
+        <v>7036029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,10 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118330814</v>
+        <v>118330820</v>
       </c>
       <c r="B21" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,38 +2664,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638757</v>
+        <v>638761</v>
       </c>
       <c r="R21" t="n">
-        <v>7036093</v>
+        <v>7036040</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,6 +2748,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27533-2024 artfynd.xlsx
+++ b/artfynd/A 27533-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118330800</v>
+        <v>118330802</v>
       </c>
       <c r="B2" t="n">
-        <v>90504</v>
+        <v>98486</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>222302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638690</v>
+        <v>638675</v>
       </c>
       <c r="R2" t="n">
-        <v>7036144</v>
+        <v>7036047</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118330816</v>
+        <v>118330824</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>97763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638747</v>
+        <v>638674</v>
       </c>
       <c r="R3" t="n">
-        <v>7036044</v>
+        <v>7036050</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118330803</v>
+        <v>118330821</v>
       </c>
       <c r="B4" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638671</v>
+        <v>638755</v>
       </c>
       <c r="R4" t="n">
-        <v>7036050</v>
+        <v>7036043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +975,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118330802</v>
+        <v>118330822</v>
       </c>
       <c r="B5" t="n">
-        <v>98486</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +1006,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222302</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Dewey</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638675</v>
+        <v>638687</v>
       </c>
       <c r="R5" t="n">
-        <v>7036047</v>
+        <v>7035989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1090,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1185,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118330821</v>
+        <v>118330806</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,50 +1223,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638755</v>
+        <v>638660</v>
       </c>
       <c r="R7" t="n">
-        <v>7036043</v>
+        <v>7036066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1295,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1415,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118330810</v>
+        <v>118330817</v>
       </c>
       <c r="B9" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,25 +1440,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638637</v>
+        <v>638710</v>
       </c>
       <c r="R9" t="n">
-        <v>7036126</v>
+        <v>7036030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118330805</v>
+        <v>118330799</v>
       </c>
       <c r="B10" t="n">
-        <v>97867</v>
+        <v>90504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1542,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638623</v>
+        <v>638684</v>
       </c>
       <c r="R10" t="n">
-        <v>7036148</v>
+        <v>7035982</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118330807</v>
+        <v>118330803</v>
       </c>
       <c r="B11" t="n">
         <v>97867</v>
@@ -1659,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638656</v>
+        <v>638671</v>
       </c>
       <c r="R11" t="n">
-        <v>7036071</v>
+        <v>7036050</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118330806</v>
+        <v>118330819</v>
       </c>
       <c r="B12" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,25 +1746,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638660</v>
+        <v>638774</v>
       </c>
       <c r="R12" t="n">
-        <v>7036066</v>
+        <v>7036029</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118330817</v>
+        <v>118330807</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,25 +1848,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1863,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638710</v>
+        <v>638656</v>
       </c>
       <c r="R13" t="n">
-        <v>7036030</v>
+        <v>7036071</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118330798</v>
+        <v>118330805</v>
       </c>
       <c r="B14" t="n">
-        <v>90504</v>
+        <v>97867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1937,25 +1950,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1965,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638811</v>
+        <v>638623</v>
       </c>
       <c r="R14" t="n">
-        <v>7036050</v>
+        <v>7036148</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118330824</v>
+        <v>118330814</v>
       </c>
       <c r="B15" t="n">
-        <v>97763</v>
+        <v>79565</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2039,25 +2052,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2067,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638674</v>
+        <v>638757</v>
       </c>
       <c r="R15" t="n">
-        <v>7036050</v>
+        <v>7036093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118330799</v>
+        <v>118330816</v>
       </c>
       <c r="B16" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2169,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638684</v>
+        <v>638747</v>
       </c>
       <c r="R16" t="n">
-        <v>7035982</v>
+        <v>7036044</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118330822</v>
+        <v>118330815</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2243,50 +2256,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638687</v>
+        <v>638768</v>
       </c>
       <c r="R17" t="n">
-        <v>7035989</v>
+        <v>7036033</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2328,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118330815</v>
+        <v>118330810</v>
       </c>
       <c r="B18" t="n">
-        <v>79565</v>
+        <v>97867</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,25 +2358,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638768</v>
+        <v>638637</v>
       </c>
       <c r="R18" t="n">
-        <v>7036033</v>
+        <v>7036126</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118330814</v>
+        <v>118330800</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>90504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638757</v>
+        <v>638690</v>
       </c>
       <c r="R19" t="n">
-        <v>7036093</v>
+        <v>7036144</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118330819</v>
+        <v>118330820</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2583,17 +2583,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638774</v>
+        <v>638761</v>
       </c>
       <c r="R20" t="n">
-        <v>7036029</v>
+        <v>7036040</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,6 +2646,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118330820</v>
+        <v>118330798</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,50 +2677,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638761</v>
+        <v>638811</v>
       </c>
       <c r="R21" t="n">
-        <v>7036040</v>
+        <v>7036050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,7 +2749,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27533-2024 artfynd.xlsx
+++ b/artfynd/A 27533-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118330815</v>
+        <v>118330810</v>
       </c>
       <c r="B17" t="n">
-        <v>79565</v>
+        <v>97867</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,25 +2256,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638768</v>
+        <v>638637</v>
       </c>
       <c r="R17" t="n">
-        <v>7036033</v>
+        <v>7036126</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118330810</v>
+        <v>118330815</v>
       </c>
       <c r="B18" t="n">
-        <v>97867</v>
+        <v>79565</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,25 +2358,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638637</v>
+        <v>638768</v>
       </c>
       <c r="R18" t="n">
-        <v>7036126</v>
+        <v>7036033</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2765,6 +2765,117 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118898335</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98486</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bäck, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>638690</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7036036</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Erixon, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27533-2024 artfynd.xlsx
+++ b/artfynd/A 27533-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118330802</v>
+        <v>118330824</v>
       </c>
       <c r="B2" t="n">
-        <v>98486</v>
+        <v>97763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222302</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638675</v>
+        <v>638674</v>
       </c>
       <c r="R2" t="n">
-        <v>7036047</v>
+        <v>7036050</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118330824</v>
+        <v>118330819</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638674</v>
+        <v>638774</v>
       </c>
       <c r="R3" t="n">
-        <v>7036050</v>
+        <v>7036029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118330821</v>
+        <v>118330803</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,50 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638755</v>
+        <v>638671</v>
       </c>
       <c r="R4" t="n">
-        <v>7036043</v>
+        <v>7036050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118330822</v>
+        <v>118330821</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1029,7 +1016,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1046,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638687</v>
+        <v>638755</v>
       </c>
       <c r="R5" t="n">
-        <v>7035989</v>
+        <v>7036043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118330811</v>
+        <v>118330810</v>
       </c>
       <c r="B6" t="n">
-        <v>90947</v>
+        <v>97867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1108,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638691</v>
+        <v>638637</v>
       </c>
       <c r="R6" t="n">
-        <v>7036144</v>
+        <v>7036126</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1313,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118330823</v>
+        <v>118330811</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>90947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,46 +1316,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638712</v>
+        <v>638691</v>
       </c>
       <c r="R8" t="n">
-        <v>7036036</v>
+        <v>7036144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1428,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118330817</v>
+        <v>118330802</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>98486</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,25 +1414,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638710</v>
+        <v>638675</v>
       </c>
       <c r="R9" t="n">
-        <v>7036030</v>
+        <v>7036047</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118330799</v>
+        <v>118330815</v>
       </c>
       <c r="B10" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,21 +1520,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638684</v>
+        <v>638768</v>
       </c>
       <c r="R10" t="n">
-        <v>7035982</v>
+        <v>7036033</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118330803</v>
+        <v>118330814</v>
       </c>
       <c r="B11" t="n">
-        <v>97867</v>
+        <v>79565</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,25 +1618,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638671</v>
+        <v>638757</v>
       </c>
       <c r="R11" t="n">
-        <v>7036050</v>
+        <v>7036093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118330819</v>
+        <v>118330817</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1774,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638774</v>
+        <v>638710</v>
       </c>
       <c r="R12" t="n">
-        <v>7036029</v>
+        <v>7036030</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118330807</v>
+        <v>118330820</v>
       </c>
       <c r="B13" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,38 +1822,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638656</v>
+        <v>638761</v>
       </c>
       <c r="R13" t="n">
-        <v>7036071</v>
+        <v>7036040</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,6 +1906,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118330805</v>
+        <v>118330823</v>
       </c>
       <c r="B14" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,38 +1937,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638623</v>
+        <v>638712</v>
       </c>
       <c r="R14" t="n">
-        <v>7036148</v>
+        <v>7036036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,6 +2021,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118330814</v>
+        <v>118330816</v>
       </c>
       <c r="B15" t="n">
         <v>79565</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638757</v>
+        <v>638747</v>
       </c>
       <c r="R15" t="n">
-        <v>7036093</v>
+        <v>7036044</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118330816</v>
+        <v>118330799</v>
       </c>
       <c r="B16" t="n">
-        <v>79565</v>
+        <v>90504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638747</v>
+        <v>638684</v>
       </c>
       <c r="R16" t="n">
-        <v>7036044</v>
+        <v>7035982</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118330810</v>
+        <v>118330800</v>
       </c>
       <c r="B17" t="n">
-        <v>97867</v>
+        <v>90504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,25 +2256,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638637</v>
+        <v>638690</v>
       </c>
       <c r="R17" t="n">
-        <v>7036126</v>
+        <v>7036144</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118330815</v>
+        <v>118330798</v>
       </c>
       <c r="B18" t="n">
-        <v>79565</v>
+        <v>90504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2362,21 +2362,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638768</v>
+        <v>638811</v>
       </c>
       <c r="R18" t="n">
-        <v>7036033</v>
+        <v>7036050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118330800</v>
+        <v>118330805</v>
       </c>
       <c r="B19" t="n">
-        <v>90504</v>
+        <v>97867</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,25 +2460,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638690</v>
+        <v>638623</v>
       </c>
       <c r="R19" t="n">
-        <v>7036144</v>
+        <v>7036148</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118330820</v>
+        <v>118330822</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638761</v>
+        <v>638687</v>
       </c>
       <c r="R20" t="n">
-        <v>7036040</v>
+        <v>7035989</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118330798</v>
+        <v>118330807</v>
       </c>
       <c r="B21" t="n">
-        <v>90504</v>
+        <v>97867</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,25 +2677,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638811</v>
+        <v>638656</v>
       </c>
       <c r="R21" t="n">
-        <v>7036050</v>
+        <v>7036071</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 27533-2024 artfynd.xlsx
+++ b/artfynd/A 27533-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118330824</v>
+        <v>118330807</v>
       </c>
       <c r="B2" t="n">
-        <v>97763</v>
+        <v>97874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638674</v>
+        <v>638656</v>
       </c>
       <c r="R2" t="n">
-        <v>7036050</v>
+        <v>7036071</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118330819</v>
+        <v>118330824</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638774</v>
+        <v>638674</v>
       </c>
       <c r="R3" t="n">
-        <v>7036029</v>
+        <v>7036050</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118330803</v>
+        <v>118330806</v>
       </c>
       <c r="B4" t="n">
-        <v>97867</v>
+        <v>97874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638671</v>
+        <v>638660</v>
       </c>
       <c r="R4" t="n">
-        <v>7036050</v>
+        <v>7036066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118330821</v>
+        <v>118330802</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>98493</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,50 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638755</v>
+        <v>638675</v>
       </c>
       <c r="R5" t="n">
-        <v>7036043</v>
+        <v>7036047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1096,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118330810</v>
+        <v>118330811</v>
       </c>
       <c r="B6" t="n">
-        <v>97867</v>
+        <v>90954</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638637</v>
+        <v>638691</v>
       </c>
       <c r="R6" t="n">
-        <v>7036126</v>
+        <v>7036144</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118330806</v>
+        <v>118330799</v>
       </c>
       <c r="B7" t="n">
-        <v>97867</v>
+        <v>90511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638660</v>
+        <v>638684</v>
       </c>
       <c r="R7" t="n">
-        <v>7036066</v>
+        <v>7035982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118330811</v>
+        <v>118330819</v>
       </c>
       <c r="B8" t="n">
-        <v>90947</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1340,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638691</v>
+        <v>638774</v>
       </c>
       <c r="R8" t="n">
-        <v>7036144</v>
+        <v>7036029</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118330802</v>
+        <v>118330817</v>
       </c>
       <c r="B9" t="n">
-        <v>98486</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222302</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638675</v>
+        <v>638710</v>
       </c>
       <c r="R9" t="n">
-        <v>7036047</v>
+        <v>7036030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118330815</v>
+        <v>118330800</v>
       </c>
       <c r="B10" t="n">
-        <v>79565</v>
+        <v>90511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1520,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638768</v>
+        <v>638690</v>
       </c>
       <c r="R10" t="n">
-        <v>7036033</v>
+        <v>7036144</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118330814</v>
+        <v>118330820</v>
       </c>
       <c r="B11" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,38 +1605,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638757</v>
+        <v>638761</v>
       </c>
       <c r="R11" t="n">
-        <v>7036093</v>
+        <v>7036040</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,6 +1689,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118330817</v>
+        <v>118330821</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,17 +1741,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638710</v>
+        <v>638755</v>
       </c>
       <c r="R12" t="n">
-        <v>7036030</v>
+        <v>7036043</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,6 +1804,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1810,10 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118330820</v>
+        <v>118330803</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,50 +1835,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638761</v>
+        <v>638671</v>
       </c>
       <c r="R13" t="n">
-        <v>7036040</v>
+        <v>7036050</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1906,7 +1907,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1925,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118330823</v>
+        <v>118330810</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1937,50 +1937,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638712</v>
+        <v>638637</v>
       </c>
       <c r="R14" t="n">
-        <v>7036036</v>
+        <v>7036126</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,7 +2009,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118330816</v>
+        <v>118330822</v>
       </c>
       <c r="B15" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,38 +2039,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638747</v>
+        <v>638687</v>
       </c>
       <c r="R15" t="n">
-        <v>7036044</v>
+        <v>7035989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,6 +2123,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118330799</v>
+        <v>118330823</v>
       </c>
       <c r="B16" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,38 +2154,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638684</v>
+        <v>638712</v>
       </c>
       <c r="R16" t="n">
-        <v>7035982</v>
+        <v>7036036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,6 +2238,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2244,10 +2257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118330800</v>
+        <v>118330816</v>
       </c>
       <c r="B17" t="n">
-        <v>90504</v>
+        <v>79572</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,21 +2273,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2284,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638690</v>
+        <v>638747</v>
       </c>
       <c r="R17" t="n">
-        <v>7036144</v>
+        <v>7036044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118330798</v>
+        <v>118330805</v>
       </c>
       <c r="B18" t="n">
-        <v>90504</v>
+        <v>97874</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,25 +2371,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2386,10 +2399,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638811</v>
+        <v>638623</v>
       </c>
       <c r="R18" t="n">
-        <v>7036050</v>
+        <v>7036148</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,10 +2461,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118330805</v>
+        <v>118330815</v>
       </c>
       <c r="B19" t="n">
-        <v>97867</v>
+        <v>79572</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,25 +2473,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2488,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638623</v>
+        <v>638768</v>
       </c>
       <c r="R19" t="n">
-        <v>7036148</v>
+        <v>7036033</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118330822</v>
+        <v>118330798</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,50 +2575,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Barrnaturskog invid Ledsjöån, söder om Önskansjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638687</v>
+        <v>638811</v>
       </c>
       <c r="R20" t="n">
-        <v>7035989</v>
+        <v>7036050</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,7 +2647,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118330807</v>
+        <v>118330814</v>
       </c>
       <c r="B21" t="n">
-        <v>97867</v>
+        <v>79572</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,25 +2677,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638656</v>
+        <v>638757</v>
       </c>
       <c r="R21" t="n">
-        <v>7036071</v>
+        <v>7036093</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
         <v>118898335</v>
       </c>
       <c r="B22" t="n">
-        <v>98486</v>
+        <v>98493</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 27533-2024 artfynd.xlsx
+++ b/artfynd/A 27533-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118330802</v>
+        <v>118330811</v>
       </c>
       <c r="B5" t="n">
-        <v>98493</v>
+        <v>90954</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222302</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638675</v>
+        <v>638691</v>
       </c>
       <c r="R5" t="n">
-        <v>7036047</v>
+        <v>7036144</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118330811</v>
+        <v>118330802</v>
       </c>
       <c r="B6" t="n">
-        <v>90954</v>
+        <v>98493</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>222302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638691</v>
+        <v>638675</v>
       </c>
       <c r="R6" t="n">
-        <v>7036144</v>
+        <v>7036047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 27533-2024 artfynd.xlsx
+++ b/artfynd/A 27533-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330800</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330801</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330811</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330814</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330815</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330816</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330824</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330817</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330819</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330820</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330821</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2069,6 +2139,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330822</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2179,6 +2254,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330823</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2276,6 +2356,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330803</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2373,6 +2458,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330805</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2470,6 +2560,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330806</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330807</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2664,6 +2764,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330809</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2761,6 +2866,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330810</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2858,6 +2968,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118330802</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2964,8 +3079,38 @@
           <t>SBF Florainventering i Ångermanland 2024</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118898335</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>